--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96677</v>
+        <v>96680</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2882,7 +2882,7 @@
         <v>136097900</v>
       </c>
       <c r="B22" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2427,7 +2427,7 @@
         <v>136097899</v>
       </c>
       <c r="B18" t="n">
-        <v>96680</v>
+        <v>96681</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2541,60 +2541,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132335525</v>
+        <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>91590</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348462</v>
+        <v>348504</v>
       </c>
       <c r="R19" t="n">
-        <v>6519162</v>
+        <v>6519183</v>
       </c>
       <c r="S19" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2618,90 +2606,98 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335525</t>
+          <t>https://artportalen.se/Sighting/136707421</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132446029</v>
+        <v>132335525</v>
       </c>
       <c r="B20" t="n">
-        <v>8374</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106540</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348623</v>
+        <v>348462</v>
       </c>
       <c r="R20" t="n">
-        <v>6519241</v>
+        <v>6519162</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2725,12 +2721,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2741,46 +2737,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132335525</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446053</v>
+        <v>132446029</v>
       </c>
       <c r="B21" t="n">
-        <v>111471</v>
+        <v>8374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,34 +2769,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348463</v>
+        <v>348623</v>
       </c>
       <c r="R21" t="n">
-        <v>6519366</v>
+        <v>6519241</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2859,6 +2845,21 @@
       <c r="AG21" t="b">
         <v>0</v>
       </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
@@ -2873,16 +2874,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446053</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136097900</v>
+        <v>132446053</v>
       </c>
       <c r="B22" t="n">
-        <v>111643</v>
+        <v>111471</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2910,14 +2911,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348618</v>
+        <v>348463</v>
       </c>
       <c r="R22" t="n">
-        <v>6519260</v>
+        <v>6519366</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2944,12 +2945,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2975,64 +2976,54 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/132446053</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>121791871</v>
+        <v>136097900</v>
       </c>
       <c r="B23" t="n">
-        <v>101326</v>
+        <v>111644</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348561</v>
+        <v>348618</v>
       </c>
       <c r="R23" t="n">
-        <v>6519216</v>
+        <v>6519260</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3056,12 +3047,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3072,36 +3063,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791871</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>121792063</v>
+        <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>101326</v>
+        <v>106399</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3109,47 +3095,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348553</v>
+        <v>348660</v>
       </c>
       <c r="R24" t="n">
-        <v>6519199</v>
+        <v>6519138</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3173,12 +3149,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,33 +3165,28 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792063</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121792253</v>
+        <v>121791871</v>
       </c>
       <c r="B25" t="n">
         <v>101326</v>
@@ -3260,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348514</v>
+        <v>348561</v>
       </c>
       <c r="R25" t="n">
-        <v>6519160</v>
+        <v>6519216</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3309,7 +3280,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3326,13 +3297,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792253</t>
+          <t>https://artportalen.se/Sighting/121791871</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121792318</v>
+        <v>121792063</v>
       </c>
       <c r="B26" t="n">
         <v>101326</v>
@@ -3377,10 +3348,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348459</v>
+        <v>348553</v>
       </c>
       <c r="R26" t="n">
-        <v>6519139</v>
+        <v>6519199</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3426,7 +3397,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3443,13 +3414,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792318</t>
+          <t>https://artportalen.se/Sighting/121792063</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121792399</v>
+        <v>121792253</v>
       </c>
       <c r="B27" t="n">
         <v>101326</v>
@@ -3494,10 +3465,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348481</v>
+        <v>348514</v>
       </c>
       <c r="R27" t="n">
-        <v>6519252</v>
+        <v>6519160</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3543,7 +3514,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3560,13 +3531,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792399</t>
+          <t>https://artportalen.se/Sighting/121792253</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121792568</v>
+        <v>121792318</v>
       </c>
       <c r="B28" t="n">
         <v>101326</v>
@@ -3607,14 +3578,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348486</v>
+        <v>348459</v>
       </c>
       <c r="R28" t="n">
-        <v>6519336</v>
+        <v>6519139</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3677,13 +3648,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792568</t>
+          <t>https://artportalen.se/Sighting/121792318</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121792607</v>
+        <v>121792399</v>
       </c>
       <c r="B29" t="n">
         <v>101326</v>
@@ -3724,14 +3695,14 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348455</v>
+        <v>348481</v>
       </c>
       <c r="R29" t="n">
-        <v>6519346</v>
+        <v>6519252</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3777,7 +3748,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3794,16 +3765,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792607</t>
+          <t>https://artportalen.se/Sighting/121792399</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132335808</v>
+        <v>121792568</v>
       </c>
       <c r="B30" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3829,16 +3800,26 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348481</v>
+        <v>348486</v>
       </c>
       <c r="R30" t="n">
-        <v>6519286</v>
+        <v>6519336</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3865,12 +3846,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3881,31 +3862,36 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335808</t>
+          <t>https://artportalen.se/Sighting/121792568</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132336006</v>
+        <v>121792607</v>
       </c>
       <c r="B31" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3931,16 +3917,26 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348550</v>
+        <v>348455</v>
       </c>
       <c r="R31" t="n">
-        <v>6519223</v>
+        <v>6519346</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3967,12 +3963,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3984,32 +3980,32 @@
       <c r="AG31" t="b">
         <v>0</v>
       </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336006</t>
+          <t>https://artportalen.se/Sighting/121792607</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132336196</v>
+        <v>132335808</v>
       </c>
       <c r="B32" t="n">
         <v>101403</v>
@@ -4040,14 +4036,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348529</v>
+        <v>348481</v>
       </c>
       <c r="R32" t="n">
-        <v>6519171</v>
+        <v>6519286</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4091,11 +4087,6 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
@@ -4110,13 +4101,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336196</t>
+          <t>https://artportalen.se/Sighting/132335808</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132336478</v>
+        <v>132336006</v>
       </c>
       <c r="B33" t="n">
         <v>101403</v>
@@ -4151,10 +4142,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348493</v>
+        <v>348550</v>
       </c>
       <c r="R33" t="n">
-        <v>6519126</v>
+        <v>6519223</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4198,6 +4189,11 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
@@ -4212,13 +4208,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336478</t>
+          <t>https://artportalen.se/Sighting/132336006</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132446046</v>
+        <v>132336196</v>
       </c>
       <c r="B34" t="n">
         <v>101403</v>
@@ -4249,17 +4245,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348506</v>
+        <v>348529</v>
       </c>
       <c r="R34" t="n">
-        <v>6519266</v>
+        <v>6519171</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4283,12 +4279,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4299,28 +4295,33 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446046</t>
+          <t>https://artportalen.se/Sighting/132336196</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132446050</v>
+        <v>132336478</v>
       </c>
       <c r="B35" t="n">
         <v>101403</v>
@@ -4351,17 +4352,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348486</v>
+        <v>348493</v>
       </c>
       <c r="R35" t="n">
-        <v>6519319</v>
+        <v>6519126</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4385,12 +4386,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4405,24 +4406,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446050</t>
+          <t>https://artportalen.se/Sighting/132336478</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446052</v>
+        <v>132446046</v>
       </c>
       <c r="B36" t="n">
         <v>101403</v>
@@ -4453,14 +4454,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348480</v>
+        <v>348506</v>
       </c>
       <c r="R36" t="n">
-        <v>6519355</v>
+        <v>6519266</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4518,16 +4519,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446052</t>
+          <t>https://artportalen.se/Sighting/132446046</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132336005</v>
+        <v>132446050</v>
       </c>
       <c r="B37" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4535,37 +4536,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348550</v>
+        <v>348486</v>
       </c>
       <c r="R37" t="n">
-        <v>6519223</v>
+        <v>6519319</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4589,12 +4590,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4605,25 +4606,229 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AI37" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132336005</v>
+      </c>
+      <c r="B39" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132336005</t>
         </is>
@@ -4667,6 +4872,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>106399</v>
+        <v>106404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>106404</v>
+        <v>106406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>91594</v>
+        <v>91596</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>106406</v>
+        <v>106412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>91596</v>
+        <v>91598</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>106412</v>
+        <v>106414</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>91598</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>106414</v>
+        <v>106415</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -2544,7 +2544,7 @@
         <v>136707421</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>91605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>136707423</v>
       </c>
       <c r="B24" t="n">
-        <v>106415</v>
+        <v>106421</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ39"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,45 +1043,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132446051</v>
+        <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>92647</v>
+        <v>89301</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1339</v>
+        <v>805</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>348495</v>
+        <v>348566</v>
       </c>
       <c r="R5" t="n">
-        <v>6519363</v>
+        <v>6519182</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1124,21 +1124,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1154,16 +1139,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446051</t>
+          <t>https://artportalen.se/Sighting/137153571</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132335997</v>
+        <v>132446051</v>
       </c>
       <c r="B6" t="n">
-        <v>96019</v>
+        <v>92647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,37 +1156,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2362</v>
+        <v>1339</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blek stjärnmossa</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mnium stellare</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>348539</v>
+        <v>348495</v>
       </c>
       <c r="R6" t="n">
-        <v>6519214</v>
+        <v>6519363</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1225,12 +1210,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,35 +1227,45 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335997</t>
+          <t>https://artportalen.se/Sighting/132446051</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132397690</v>
+        <v>132335997</v>
       </c>
       <c r="B7" t="n">
-        <v>97888</v>
+        <v>96019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,21 +1273,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2604</v>
+        <v>2362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Trädporella</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porella platyphylla</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Pfeiff.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1368,16 +1363,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132397690</t>
+          <t>https://artportalen.se/Sighting/132335997</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132336000</v>
+        <v>132397690</v>
       </c>
       <c r="B8" t="n">
-        <v>96512</v>
+        <v>97888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1385,21 +1380,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2667</v>
+        <v>2604</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Trädporella</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Porella platyphylla</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(L.) Pfeiff.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1475,13 +1470,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336000</t>
+          <t>https://artportalen.se/Sighting/132397690</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132446044</v>
+        <v>132336000</v>
       </c>
       <c r="B9" t="n">
         <v>96512</v>
@@ -1512,17 +1507,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>348545</v>
+        <v>348539</v>
       </c>
       <c r="R9" t="n">
-        <v>6519237</v>
+        <v>6519214</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1546,12 +1541,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,31 +1557,36 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446044</t>
+          <t>https://artportalen.se/Sighting/132336000</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132335807</v>
+        <v>132446044</v>
       </c>
       <c r="B10" t="n">
-        <v>96501</v>
+        <v>96512</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1594,37 +1594,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2671</v>
+        <v>2667</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>348516</v>
+        <v>348545</v>
       </c>
       <c r="R10" t="n">
-        <v>6519293</v>
+        <v>6519237</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,33 +1664,28 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>På ek.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335807</t>
+          <t>https://artportalen.se/Sighting/132446044</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132446043</v>
+        <v>132335807</v>
       </c>
       <c r="B11" t="n">
         <v>96501</v>
@@ -1721,17 +1716,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, 60 m O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>348552</v>
+        <v>348516</v>
       </c>
       <c r="R11" t="n">
-        <v>6519205</v>
+        <v>6519293</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1755,12 +1750,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1771,28 +1766,33 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>På ek.</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446043</t>
+          <t>https://artportalen.se/Sighting/132335807</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132446047</v>
+        <v>132446043</v>
       </c>
       <c r="B12" t="n">
         <v>96501</v>
@@ -1827,10 +1827,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>348480</v>
+        <v>348552</v>
       </c>
       <c r="R12" t="n">
-        <v>6519264</v>
+        <v>6519205</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1888,13 +1888,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446047</t>
+          <t>https://artportalen.se/Sighting/132446043</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132446048</v>
+        <v>132446047</v>
       </c>
       <c r="B13" t="n">
         <v>96501</v>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>348482</v>
+        <v>348480</v>
       </c>
       <c r="R13" t="n">
-        <v>6519312</v>
+        <v>6519264</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1990,16 +1990,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446048</t>
+          <t>https://artportalen.se/Sighting/132446047</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132397692</v>
+        <v>132446048</v>
       </c>
       <c r="B14" t="n">
-        <v>96261</v>
+        <v>96501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2007,37 +2007,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2676</v>
+        <v>2671</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>348539</v>
+        <v>348482</v>
       </c>
       <c r="R14" t="n">
-        <v>6519214</v>
+        <v>6519312</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2077,36 +2077,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132397692</t>
+          <t>https://artportalen.se/Sighting/132446048</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132335999</v>
+        <v>132397692</v>
       </c>
       <c r="B15" t="n">
-        <v>96306</v>
+        <v>96261</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2114,21 +2109,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2779</v>
+        <v>2676</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Guldlockmossa</t>
+          <t>Grov baronmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Homalothecium sericeum</t>
+          <t>Anomodon viticulosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2204,13 +2199,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335999</t>
+          <t>https://artportalen.se/Sighting/132397692</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132446045</v>
+        <v>132335999</v>
       </c>
       <c r="B16" t="n">
         <v>96306</v>
@@ -2241,17 +2236,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>348545</v>
+        <v>348539</v>
       </c>
       <c r="R16" t="n">
-        <v>6519237</v>
+        <v>6519214</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2275,12 +2270,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2291,31 +2286,36 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446045</t>
+          <t>https://artportalen.se/Sighting/132335999</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132335439</v>
+        <v>132446045</v>
       </c>
       <c r="B17" t="n">
-        <v>96533</v>
+        <v>96306</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2323,37 +2323,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2818</v>
+        <v>2779</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Guldlockmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Homalothecium sericeum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Hedw.) Schimp.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>348505</v>
+        <v>348545</v>
       </c>
       <c r="R17" t="n">
-        <v>6519139</v>
+        <v>6519237</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2377,12 +2377,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2393,41 +2393,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Äldre blandskog, gran med mycket lövinslag.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Grov, murken granlåga.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335439</t>
+          <t>https://artportalen.se/Sighting/132446045</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136097899</v>
+        <v>132335439</v>
       </c>
       <c r="B18" t="n">
-        <v>96681</v>
+        <v>96533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2455,17 +2445,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Vandringstjärnet, öster om norra delen, nära Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>348719</v>
+        <v>348505</v>
       </c>
       <c r="R18" t="n">
-        <v>6519093</v>
+        <v>6519139</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2489,12 +2479,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2506,80 +2496,75 @@
       <c r="AG18" t="b">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Äldre blandskog, gran med mycket lövinslag.</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Grov, murken granlåga.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097899</t>
+          <t>https://artportalen.se/Sighting/132335439</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136707421</v>
+        <v>136097899</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>96681</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5741</v>
+        <v>2818</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) R. H. Petersen</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>348504</v>
+        <v>348719</v>
       </c>
       <c r="R19" t="n">
-        <v>6519183</v>
+        <v>6519093</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2606,23 +2591,37 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2638,66 +2637,54 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707421</t>
+          <t>https://artportalen.se/Sighting/136097899</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132335525</v>
+        <v>136707421</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>91609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>5741</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>348462</v>
+        <v>348504</v>
       </c>
       <c r="R20" t="n">
-        <v>6519162</v>
+        <v>6519183</v>
       </c>
       <c r="S20" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2721,90 +2708,98 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335525</t>
+          <t>https://artportalen.se/Sighting/136707421</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132446029</v>
+        <v>132335525</v>
       </c>
       <c r="B21" t="n">
-        <v>8374</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106540</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Svart askbastborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hylesinus crenatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fabricius, 1787)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Dls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>348623</v>
+        <v>348462</v>
       </c>
       <c r="R21" t="n">
-        <v>6519241</v>
+        <v>6519162</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2828,12 +2823,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2844,46 +2839,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>ask</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446029</t>
+          <t>https://artportalen.se/Sighting/132335525</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132446053</v>
+        <v>132446029</v>
       </c>
       <c r="B22" t="n">
-        <v>111471</v>
+        <v>8374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2891,34 +2871,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219711</v>
+        <v>106540</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Svart askbastborre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hylesinus crenatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fabricius, 1787)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>348463</v>
+        <v>348623</v>
       </c>
       <c r="R22" t="n">
-        <v>6519366</v>
+        <v>6519241</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2962,6 +2947,21 @@
       <c r="AG22" t="b">
         <v>0</v>
       </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446053</t>
+          <t>https://artportalen.se/Sighting/132446029</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136097900</v>
+        <v>132446053</v>
       </c>
       <c r="B23" t="n">
-        <v>111644</v>
+        <v>111471</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,14 +3013,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Väst om Rannebergets naturreservat, Dls</t>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>348618</v>
+        <v>348463</v>
       </c>
       <c r="R23" t="n">
-        <v>6519260</v>
+        <v>6519366</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3047,12 +3047,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3078,33 +3078,33 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136097900</t>
+          <t>https://artportalen.se/Sighting/132446053</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136707423</v>
+        <v>136097900</v>
       </c>
       <c r="B24" t="n">
-        <v>106421</v>
+        <v>111644</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221141</v>
+        <v>219711</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3115,14 +3115,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Väster om Rannebergets NR, Dls</t>
+          <t>Väst om Rannebergets naturreservat, Dls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>348660</v>
+        <v>348618</v>
       </c>
       <c r="R24" t="n">
-        <v>6519138</v>
+        <v>6519260</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3149,12 +3149,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3180,64 +3180,54 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136707423</t>
+          <t>https://artportalen.se/Sighting/136097900</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>121791871</v>
+        <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>101326</v>
+        <v>111670</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>219711</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Ranneberget, Dls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>348561</v>
+        <v>348464</v>
       </c>
       <c r="R25" t="n">
-        <v>6519216</v>
+        <v>6519341</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3261,12 +3251,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3277,36 +3267,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121791871</t>
+          <t>https://artportalen.se/Sighting/137153573</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121792063</v>
+        <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>101326</v>
+        <v>106425</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3314,47 +3299,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>221141</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
+          <t>Väster om Rannebergets NR, Dls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>348553</v>
+        <v>348660</v>
       </c>
       <c r="R26" t="n">
-        <v>6519199</v>
+        <v>6519138</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3378,12 +3353,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-12-30</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3394,33 +3369,28 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Barr-/lövbland</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792063</t>
+          <t>https://artportalen.se/Sighting/136707423</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121792253</v>
+        <v>121791871</v>
       </c>
       <c r="B27" t="n">
         <v>101326</v>
@@ -3465,10 +3435,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>348514</v>
+        <v>348561</v>
       </c>
       <c r="R27" t="n">
-        <v>6519160</v>
+        <v>6519216</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3514,7 +3484,7 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3531,13 +3501,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792253</t>
+          <t>https://artportalen.se/Sighting/121791871</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>121792318</v>
+        <v>121792063</v>
       </c>
       <c r="B28" t="n">
         <v>101326</v>
@@ -3582,10 +3552,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>348459</v>
+        <v>348553</v>
       </c>
       <c r="R28" t="n">
-        <v>6519139</v>
+        <v>6519199</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3631,7 +3601,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -3648,13 +3618,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792318</t>
+          <t>https://artportalen.se/Sighting/121792063</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>121792399</v>
+        <v>121792253</v>
       </c>
       <c r="B29" t="n">
         <v>101326</v>
@@ -3699,10 +3669,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>348481</v>
+        <v>348514</v>
       </c>
       <c r="R29" t="n">
-        <v>6519252</v>
+        <v>6519160</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3748,7 +3718,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Barr-/lövbland</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3765,13 +3735,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792399</t>
+          <t>https://artportalen.se/Sighting/121792253</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>121792568</v>
+        <v>121792318</v>
       </c>
       <c r="B30" t="n">
         <v>101326</v>
@@ -3812,14 +3782,14 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>348486</v>
+        <v>348459</v>
       </c>
       <c r="R30" t="n">
-        <v>6519336</v>
+        <v>6519139</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3882,13 +3852,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792568</t>
+          <t>https://artportalen.se/Sighting/121792318</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>121792607</v>
+        <v>121792399</v>
       </c>
       <c r="B31" t="n">
         <v>101326</v>
@@ -3929,14 +3899,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Janses kulle, Janses kulle, Dls</t>
+          <t>Skårdalens gamla tomt, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>348455</v>
+        <v>348481</v>
       </c>
       <c r="R31" t="n">
-        <v>6519346</v>
+        <v>6519252</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3982,7 +3952,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barr-/lövbland</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3999,16 +3969,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121792607</t>
+          <t>https://artportalen.se/Sighting/121792399</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132335808</v>
+        <v>121792568</v>
       </c>
       <c r="B32" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4034,16 +4004,26 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Vandringstjärnet, O nordänden, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>348481</v>
+        <v>348486</v>
       </c>
       <c r="R32" t="n">
-        <v>6519286</v>
+        <v>6519336</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4070,12 +4050,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4086,31 +4066,36 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132335808</t>
+          <t>https://artportalen.se/Sighting/121792568</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132336006</v>
+        <v>121792607</v>
       </c>
       <c r="B33" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4136,16 +4121,26 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Janses kulle, Janses kulle, Dls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>348550</v>
+        <v>348455</v>
       </c>
       <c r="R33" t="n">
-        <v>6519223</v>
+        <v>6519346</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4172,12 +4167,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4189,32 +4184,32 @@
       <c r="AG33" t="b">
         <v>0</v>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336006</t>
+          <t>https://artportalen.se/Sighting/121792607</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132336196</v>
+        <v>132335808</v>
       </c>
       <c r="B34" t="n">
         <v>101403</v>
@@ -4245,14 +4240,14 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet, O nordänden, Dls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>348529</v>
+        <v>348481</v>
       </c>
       <c r="R34" t="n">
-        <v>6519171</v>
+        <v>6519286</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4296,11 +4291,6 @@
       <c r="AG34" t="b">
         <v>0</v>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
-      </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
@@ -4315,13 +4305,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336196</t>
+          <t>https://artportalen.se/Sighting/132335808</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132336478</v>
+        <v>132336006</v>
       </c>
       <c r="B35" t="n">
         <v>101403</v>
@@ -4356,10 +4346,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>348493</v>
+        <v>348550</v>
       </c>
       <c r="R35" t="n">
-        <v>6519126</v>
+        <v>6519223</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4403,6 +4393,11 @@
       <c r="AG35" t="b">
         <v>0</v>
       </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
@@ -4417,13 +4412,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132336478</t>
+          <t>https://artportalen.se/Sighting/132336006</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132446046</v>
+        <v>132336196</v>
       </c>
       <c r="B36" t="n">
         <v>101403</v>
@@ -4454,17 +4449,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>348506</v>
+        <v>348529</v>
       </c>
       <c r="R36" t="n">
-        <v>6519266</v>
+        <v>6519171</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4488,12 +4483,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4504,28 +4499,33 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446046</t>
+          <t>https://artportalen.se/Sighting/132336196</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132446050</v>
+        <v>132336478</v>
       </c>
       <c r="B37" t="n">
         <v>101403</v>
@@ -4556,17 +4556,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väst om Skårdalens gamla tomt, Dls</t>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>348486</v>
+        <v>348493</v>
       </c>
       <c r="R37" t="n">
-        <v>6519319</v>
+        <v>6519126</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4590,12 +4590,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4610,24 +4610,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anton Larsson</t>
+          <t>Leif Appelgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446050</t>
+          <t>https://artportalen.se/Sighting/132336478</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132446052</v>
+        <v>132446046</v>
       </c>
       <c r="B38" t="n">
         <v>101403</v>
@@ -4658,14 +4658,14 @@
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Skog norr om Vandringstjärnet, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>348480</v>
+        <v>348506</v>
       </c>
       <c r="R38" t="n">
-        <v>6519355</v>
+        <v>6519266</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4723,16 +4723,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132446052</t>
+          <t>https://artportalen.se/Sighting/132446046</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132336005</v>
+        <v>132446050</v>
       </c>
       <c r="B39" t="n">
-        <v>101324</v>
+        <v>101403</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4740,37 +4740,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>222782</v>
+        <v>222498</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+          <t>Väst om Skårdalens gamla tomt, Dls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>348550</v>
+        <v>348486</v>
       </c>
       <c r="R39" t="n">
-        <v>6519223</v>
+        <v>6519319</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4794,12 +4794,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4810,25 +4810,331 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AI39" t="inlineStr">
-        <is>
-          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Leif Appelgren</t>
+          <t>Anton Larsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446050</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132446052</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Skog norr om Vandringstjärnet, Dls</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>348480</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6519355</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132446052</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137153572</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101582</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Väst om Ranneberget, Dls</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>348456</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6519159</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anton Larsson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137153572</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>132336005</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Vandringstjärnet NO, Skårdalens gamla tomt, Dls</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>348550</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6519223</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Mellerud</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Dalskog</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Lövrikt område vid gammal torp-/kulturmark.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132336005</t>
         </is>
@@ -4874,6 +5180,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>106425</v>
+        <v>106427</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89301</v>
+        <v>89303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136707421</v>
       </c>
       <c r="B20" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>106427</v>
+        <v>106429</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89303</v>
+        <v>89316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136707421</v>
       </c>
       <c r="B20" t="n">
-        <v>91611</v>
+        <v>91624</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>106429</v>
+        <v>106442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136707421</v>
       </c>
       <c r="B20" t="n">
-        <v>91624</v>
+        <v>91626</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>106442</v>
+        <v>106444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89318</v>
+        <v>89321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136707421</v>
       </c>
       <c r="B20" t="n">
-        <v>91626</v>
+        <v>91629</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>106444</v>
+        <v>106448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89321</v>
+        <v>89331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>136707421</v>
       </c>
       <c r="B20" t="n">
-        <v>91629</v>
+        <v>91639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>136707423</v>
       </c>
       <c r="B26" t="n">
-        <v>106448</v>
+        <v>106467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89332</v>
+        <v>89335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89335</v>
+        <v>89340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89340</v>
+        <v>89351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89351</v>
+        <v>89352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 53515-2024 artfynd.xlsx
+++ b/artfynd/A 53515-2024 artfynd.xlsx
@@ -1046,7 +1046,7 @@
         <v>137153571</v>
       </c>
       <c r="B5" t="n">
-        <v>89355</v>
+        <v>89359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -3189,7 +3189,7 @@
         <v>137153573</v>
       </c>
       <c r="B25" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>137153572</v>
       </c>
       <c r="B41" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
